--- a/GWD Data/Services.xlsx
+++ b/GWD Data/Services.xlsx
@@ -1,17 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="9302"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView xWindow="240" yWindow="120" windowWidth="14940" windowHeight="9225" activeTab="0"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Services" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="43">
   <si>
     <t>Sl. No</t>
   </si>
@@ -122,29 +126,49 @@
   </si>
   <si>
     <t>Water Quality Testing (Industrial)</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>Water Quality Testing Including Bacteriology (Domestic)</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>Water Quality Testing Including Bacteriology (Industrial)</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>110mm (4.5") Borewell Drilling with Subsidy</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="3">
     <font>
-      <sz val="10.0"/>
-      <color rgb="FF000000"/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Cambria"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Merriweather"/>
-    </font>
-    <font>
-      <sz val="12.0"/>
-      <color theme="1"/>
-      <name val="Merriweather"/>
+      <name val="Cambria"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -152,11 +176,17 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="3">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -172,6 +202,7 @@
       </bottom>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -183,154 +214,332 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="15" builtinId="5"/>
+    <cellStyle name="Currency" xfId="16" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
+    <cellStyle name="Comma" xfId="18" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="3">
     <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF4DD0E1"/>
           <bgColor rgb="FF4DD0E1"/>
         </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font/>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFFFFF"/>
           <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font/>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFE0F7FA"/>
           <bgColor rgb="FFE0F7FA"/>
         </patternFill>
       </fill>
-      <border/>
     </dxf>
   </dxfs>
-  <tableStyles count="1">
-    <tableStyle count="3" pivot="0" name="Services-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Services-style" pivot="0" table="0" count="3">
+      <tableStyleElement type="headerRow" dxfId="0"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="2"/>
     </tableStyle>
   </tableStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D15" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_8" displayName="Table_8" ref="A1:D18">
   <tableColumns count="4">
-    <tableColumn name="Sl. No" id="1"/>
-    <tableColumn name="Item Name" id="2"/>
-    <tableColumn name="Unit" id="3"/>
-    <tableColumn name="Rate" id="4"/>
+    <tableColumn id="1" name="Sl. No"/>
+    <tableColumn id="2" name="Item Name"/>
+    <tableColumn id="3" name="Unit"/>
+    <tableColumn id="4" name="Rate"/>
   </tableColumns>
-  <tableStyleInfo name="Services-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Services-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Sheets">
+    <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="000000"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4285F4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EA4335"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="FBBC04"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="34A853"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="FF6D01"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="46BDC6"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Sheets">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -471,24 +680,22 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <tabColor rgb="FFFF00FF"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" width="5.38"/>
-    <col customWidth="1" min="2" max="2" width="43.25"/>
-    <col customWidth="1" min="3" max="3" width="12.75"/>
-    <col customWidth="1" min="4" max="4" width="6.25"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC724BCE-E3E5-4ED3-9FC4-A2D3BA76B9A6}">
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" ht="12.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -502,7 +709,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4" ht="12.75">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -513,10 +720,10 @@
         <v>6</v>
       </c>
       <c r="D2" s="6">
-        <v>585.0</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="12.75">
       <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
@@ -527,10 +734,10 @@
         <v>6</v>
       </c>
       <c r="D3" s="6">
-        <v>1935.0</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>1935</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="12.75">
       <c r="A4" s="4" t="s">
         <v>9</v>
       </c>
@@ -541,10 +748,10 @@
         <v>6</v>
       </c>
       <c r="D4" s="6">
-        <v>3860.0</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>3860</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="12.75">
       <c r="A5" s="4" t="s">
         <v>11</v>
       </c>
@@ -555,10 +762,10 @@
         <v>13</v>
       </c>
       <c r="D5" s="6">
-        <v>14475.0</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>14475</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="12.75">
       <c r="A6" s="4" t="s">
         <v>14</v>
       </c>
@@ -569,10 +776,10 @@
         <v>16</v>
       </c>
       <c r="D6" s="6">
-        <v>390.0</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="12.75">
       <c r="A7" s="4" t="s">
         <v>17</v>
       </c>
@@ -583,10 +790,10 @@
         <v>16</v>
       </c>
       <c r="D7" s="6">
-        <v>665.0</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="12.75">
       <c r="A8" s="4" t="s">
         <v>19</v>
       </c>
@@ -597,10 +804,10 @@
         <v>16</v>
       </c>
       <c r="D8" s="6">
-        <v>2315.0</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>2315</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="12.75">
       <c r="A9" s="4" t="s">
         <v>21</v>
       </c>
@@ -611,10 +818,10 @@
         <v>16</v>
       </c>
       <c r="D9" s="6">
-        <v>2980.0</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>2980</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="12.75">
       <c r="A10" s="4" t="s">
         <v>23</v>
       </c>
@@ -625,10 +832,10 @@
         <v>16</v>
       </c>
       <c r="D10" s="6">
-        <v>255.0</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="12.75">
       <c r="A11" s="4" t="s">
         <v>25</v>
       </c>
@@ -639,10 +846,10 @@
         <v>27</v>
       </c>
       <c r="D11" s="6">
-        <v>5790.0</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>5790</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="12.75">
       <c r="A12" s="4" t="s">
         <v>28</v>
       </c>
@@ -653,10 +860,10 @@
         <v>27</v>
       </c>
       <c r="D12" s="6">
-        <v>15435.0</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>15435</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="12.75">
       <c r="A13" s="4" t="s">
         <v>30</v>
       </c>
@@ -667,10 +874,10 @@
         <v>27</v>
       </c>
       <c r="D13" s="6">
-        <v>2870.0</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>2870</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="12.75">
       <c r="A14" s="4" t="s">
         <v>32</v>
       </c>
@@ -681,10 +888,10 @@
         <v>34</v>
       </c>
       <c r="D14" s="6">
-        <v>445.0</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="12.75">
       <c r="A15" s="4" t="s">
         <v>35</v>
       </c>
@@ -695,16 +902,56 @@
         <v>34</v>
       </c>
       <c r="D15" s="6">
-        <v>1105.0</v>
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="12.75">
+      <c r="A16" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" s="6">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="12.75">
+      <c r="A17" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" s="6">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="12.75">
+      <c r="A18" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="6">
+        <f>D6/2</f>
+        <v>195</v>
       </c>
     </row>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.354166666666667" footer="0.0" header="0.0" left="0.708333333333333" right="0.315277777777778" top="0.551388888888889"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
--- a/GWD Data/Services.xlsx
+++ b/GWD Data/Services.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="45">
   <si>
     <t>Sl. No</t>
   </si>
@@ -144,6 +144,12 @@
   </si>
   <si>
     <t>110mm (4.5") Borewell Drilling with Subsidy</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>Rotary cum DTH OB Drilling</t>
   </si>
 </sst>
 </file>
@@ -384,7 +390,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_8" displayName="Table_8" ref="A1:D18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_8" displayName="Table_8" ref="A1:D19">
   <tableColumns count="4">
     <tableColumn id="1" name="Sl. No"/>
     <tableColumn id="2" name="Item Name"/>
@@ -691,8 +697,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC724BCE-E3E5-4ED3-9FC4-A2D3BA76B9A6}">
-  <dimension ref="A1:D18"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07805C1F-F88E-47FC-92BE-6058314FB9A6}">
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
     <row r="1" spans="1:4" ht="12.75">
@@ -946,6 +952,20 @@
       <c r="D18" s="6">
         <f>D6/2</f>
         <v>195</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="12.75">
+      <c r="A19" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="6">
+        <v>1985</v>
       </c>
     </row>
   </sheetData>

--- a/GWD Data/Services.xlsx
+++ b/GWD Data/Services.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="48">
   <si>
     <t>Sl. No</t>
   </si>
@@ -150,6 +150,15 @@
   </si>
   <si>
     <t>Rotary cum DTH OB Drilling</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>Pumping Test</t>
+  </si>
+  <si>
+    <t>5 hrs</t>
   </si>
 </sst>
 </file>
@@ -185,7 +194,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -207,18 +216,6 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -245,15 +242,12 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -390,7 +384,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_8" displayName="Table_8" ref="A1:D19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_7" displayName="Table_7" ref="A1:D20">
   <tableColumns count="4">
     <tableColumn id="1" name="Sl. No"/>
     <tableColumn id="2" name="Item Name"/>
@@ -697,275 +691,289 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07805C1F-F88E-47FC-92BE-6058314FB9A6}">
-  <dimension ref="A1:D19"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB1C56C4-C1B2-4CAD-A1DD-E57BE86AB9A6}">
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
     <row r="1" spans="1:4" ht="12.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="12.75">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="5">
         <v>585</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="12.75">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="5">
         <v>1935</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="12.75">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <v>3860</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="12.75">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <v>14475</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="12.75">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <v>390</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="12.75">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <v>665</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="12.75">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <v>2315</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="12.75">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="5">
         <v>2980</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="12.75">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="5">
         <v>255</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="12.75">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="5">
         <v>5790</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="12.75">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="5">
         <v>15435</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="12.75">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="5">
         <v>2870</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="12.75">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="5">
         <v>445</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="12.75">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="5">
         <v>1105</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="12.75">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="5">
         <v>670</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="12.75">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="5">
         <v>1330</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="12.75">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="5">
         <f>D6/2</f>
         <v>195</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="12.75">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="5">
         <v>1985</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="12.75">
+      <c r="A20" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" s="5">
+        <v>7490</v>
       </c>
     </row>
   </sheetData>
